--- a/agent/flows/search-export/RuntimeSearchResults.template.xlsx
+++ b/agent/flows/search-export/RuntimeSearchResults.template.xlsx
@@ -12,18 +12,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Results'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Results'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Results'!$A$1:$J$9</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=";;;&quot;Open file&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,7 +41,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="23"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -67,13 +68,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0025364B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="000563C1"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
@@ -134,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,20 +157,29 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
@@ -272,14 +277,29 @@
         <t>Open file links to the original. The full URL remains in the cell value; SourceSite is preserved in hidden column F.</t>
       </text>
     </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>Source File.TimeCreated in UTC, not export or site-collection creation time. Blank means the source did not supply it.</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>Real Excel UTC calendar date derived from hidden CreatedUTC. The full source timestamp remains unchanged there.</t>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0" shapeId="0">
+      <text>
+        <t>Real Excel UTC calendar date derived from hidden ModifiedUTC. The full source timestamp remains unchanged there.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SearchResults" displayName="SearchResults" ref="A8:H9" headerRowCount="1">
-  <autoFilter ref="A8:H9"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SearchResults" displayName="SearchResults" ref="A8:K9" headerRowCount="1">
+  <autoFilter ref="A8:K9"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="Department"/>
     <tableColumn id="3" name="Tags"/>
@@ -289,7 +309,14 @@
     <tableColumn id="7" name="URL">
       <calculatedColumnFormula>IF(SearchResults[[#This Row],[SourceURL]]="","",HYPERLINK(SearchResults[[#This Row],[SourceURL]],SearchResults[[#This Row],[SourceURL]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="SourceURL"/>
+    <tableColumn id="8" name="CreatedUTC"/>
+    <tableColumn id="9" name="Created (UTC)">
+      <calculatedColumnFormula>IF(SearchResults[[#This Row],[CreatedUTC]]="","Not supplied",DATE(VALUE(LEFT(SearchResults[[#This Row],[CreatedUTC]],4)),VALUE(MID(SearchResults[[#This Row],[CreatedUTC]],6,2)),VALUE(MID(SearchResults[[#This Row],[CreatedUTC]],9,2))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" name="Modified (UTC)">
+      <calculatedColumnFormula>IF(SearchResults[[#This Row],[ModifiedUTC]]="","Not supplied",DATE(VALUE(LEFT(SearchResults[[#This Row],[ModifiedUTC]],4)),VALUE(MID(SearchResults[[#This Row],[ModifiedUTC]],6,2)),VALUE(MID(SearchResults[[#This Row],[ModifiedUTC]],9,2))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" name="SourceURL"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -595,66 +622,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="24" customWidth="1" min="5" max="5"/>
     <col hidden="1" width="38" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" style="1" min="7" max="7"/>
-    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col hidden="1" width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="80" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>CorpNet Search Results</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1"/>
-    <row r="3" ht="26" customHeight="1">
+    <row r="2" ht="2" customHeight="1"/>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>PRIVATE SEARCH EXPORT | FILES AND PAGES</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>SCOPE</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Full query and scope: ExportInfo tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>SEARCH</t>
+        </is>
+      </c>
+      <c r="B4" s="7">
+        <f>"Scope: "&amp;IFERROR(IF(INDEX(ExportMetadata[Value],MATCH("Scope",ExportMetadata[Field],0))="","",INDEX(ExportMetadata[Value],MATCH("Scope",ExportMetadata[Field],0))),"")&amp;" | Query: "&amp;IFERROR(IF(INDEX(ExportMetadata[Value],MATCH("Query",ExportMetadata[Field],0))="","",INDEX(ExportMetadata[Value],MATCH("Query",ExportMetadata[Field],0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Exact row count and completion details: ExportInfo tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>RESULTS</t>
+        </is>
+      </c>
+      <c r="B5" s="7">
+        <f>"Rows: "&amp;IFERROR(IF(INDEX(ExportMetadata[Value],MATCH("ExportedRowCount",ExportMetadata[Field],0))="","",INDEX(ExportMetadata[Value],MATCH("ExportedRowCount",ExportMetadata[Field],0))),"")&amp;" | Files: "&amp;IFERROR(IF(INDEX(ExportMetadata[Value],MATCH("FileCount",ExportMetadata[Field],0))="","",INDEX(ExportMetadata[Value],MATCH("FileCount",ExportMetadata[Field],0))),"")&amp;" | Pages: "&amp;IFERROR(IF(INDEX(ExportMetadata[Value],MATCH("PageCount",ExportMetadata[Field],0))="","",INDEX(ExportMetadata[Value],MATCH("PageCount",ExportMetadata[Field],0))),"")&amp;" | Status: "&amp;IFERROR(IF(INDEX(ExportMetadata[Value],MATCH("CompletionStatus",ExportMetadata[Field],0))="","",INDEX(ExportMetadata[Value],MATCH("CompletionStatus",ExportMetadata[Field],0))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Use the header filters to narrow results. Select Open file to view the original. Full export details: ExportInfo tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="9" customHeight="1">
+          <t>Filter any column. Open file checks current access. Full timestamps are retained in hidden columns; details: ExportInfo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="3" customHeight="1">
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -662,8 +690,9 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Title</t>
@@ -699,36 +728,60 @@
           <t>URL</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>CreatedUTC</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Created (UTC)</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Modified (UTC)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>SourceURL</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>__CORPNET_EMPTY_EXPORT__</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
+      <c r="B9" s="11" t="n"/>
       <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="11">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="12">
         <f>IF(SearchResults[[#This Row],[SourceURL]]="","",HYPERLINK(SearchResults[[#This Row],[SourceURL]],SearchResults[[#This Row],[SourceURL]]))</f>
         <v/>
       </c>
-      <c r="H9" s="10" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="16">
+        <f>IF(SearchResults[[#This Row],[CreatedUTC]]="","Not supplied",DATE(VALUE(LEFT(SearchResults[[#This Row],[CreatedUTC]],4)),VALUE(MID(SearchResults[[#This Row],[CreatedUTC]],6,2)),VALUE(MID(SearchResults[[#This Row],[CreatedUTC]],9,2))))</f>
+        <v/>
+      </c>
+      <c r="J9" s="16">
+        <f>IF(SearchResults[[#This Row],[ModifiedUTC]]="","Not supplied",DATE(VALUE(LEFT(SearchResults[[#This Row],[ModifiedUTC]],4)),VALUE(MID(SearchResults[[#This Row],[ModifiedUTC]],6,2)),VALUE(MID(SearchResults[[#This Row],[ModifiedUTC]],9,2))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="B4:J4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
@@ -762,108 +815,108 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Query</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr"/>
+      <c r="B2" s="18" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr"/>
+      <c r="B3" s="18" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>RequestedBy</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr"/>
+      <c r="B4" s="18" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>GeneratedUTC</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr"/>
+      <c r="B5" s="18" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>CompletionStatus</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>CountSemantics</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr"/>
+      <c r="B7" s="18" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Sharing</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr"/>
+      <c r="B8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Snapshot</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>TextSafety</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="57" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>JobId</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -871,7 +924,7 @@
           <t>ExportedRowCount</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr"/>
+      <c r="B13" s="19" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -879,7 +932,7 @@
           <t>EstimatedIndexMatches</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr"/>
+      <c r="B14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -887,7 +940,7 @@
           <t>UpstreamComplete</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr"/>
+      <c r="B15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -895,7 +948,7 @@
           <t>WriterRowCap</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr"/>
+      <c r="B16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -903,7 +956,7 @@
           <t>OmittedRowCount</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr"/>
+      <c r="B17" s="19" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +964,7 @@
           <t>ProcessingErrors</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr"/>
+      <c r="B18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -919,7 +972,7 @@
           <t>CompletionDetail</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -927,7 +980,7 @@
           <t>TruncatedUpstream</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr"/>
+      <c r="B20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -935,7 +988,7 @@
           <t>SourceTypes</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr"/>
+      <c r="B21" s="19" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -943,7 +996,7 @@
           <t>FileCount</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr"/>
+      <c r="B22" s="19" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -951,7 +1004,7 @@
           <t>PageCount</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr"/>
+      <c r="B23" s="19" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -959,7 +1012,7 @@
           <t>DuplicateIndexHits</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr"/>
+      <c r="B24" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
